--- a/Data/Estimated.prev.2016-2023.xlsx
+++ b/Data/Estimated.prev.2016-2023.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\toro2\OneDrive\Documentos\OBEMET Centro de Obesidad y Salud Metabólica\Artículos\Incidencia Diabetes Peru Colombia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Toennies\Incidence_LATAM\Incidence-Peru\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8D5AAD-F540-4F8F-9CF8-42138ED5D986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="7" xr2:uid="{E9509A47-FCBB-49E0-86FD-3F37B3D1E964}"/>
+    <workbookView xWindow="-19305" yWindow="-105" windowWidth="19425" windowHeight="10305" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="2023" sheetId="1" r:id="rId1"/>
@@ -22,7 +21,7 @@
     <sheet name="2017" sheetId="7" r:id="rId7"/>
     <sheet name="2016" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,10 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="20">
-  <si>
-    <t>SEXO</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="19">
   <si>
     <t>BAND</t>
   </si>
@@ -108,8 +104,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,7 +149,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -484,36 +480,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35C3C853-2902-418D-A18C-5449E242D687}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
       <c r="C2">
         <v>0.91773278308355377</v>
@@ -525,12 +521,12 @@
         <v>2.0440002598724329</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>0.54120808731764714</v>
@@ -542,12 +538,12 @@
         <v>0.85079503364887177</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>0.51510761442953845</v>
@@ -559,12 +555,12 @@
         <v>0.91286429613253917</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>0.91063686944053146</v>
@@ -576,12 +572,12 @@
         <v>1.3555712298749549</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>2.0098565066447782</v>
@@ -593,12 +589,12 @@
         <v>2.728452330363039</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>3.894286843349644</v>
@@ -610,12 +606,12 @@
         <v>5.1936139505662169</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>6.6119866460441683</v>
@@ -627,12 +623,12 @@
         <v>8.1952521797877225</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>9.4527573715397626</v>
@@ -644,12 +640,12 @@
         <v>11.23237754470613</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>11.92596077322886</v>
@@ -661,12 +657,12 @@
         <v>14.0942264990359</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>13.324350701995559</v>
@@ -678,12 +674,12 @@
         <v>15.71280457946585</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>13.473413284439181</v>
@@ -695,12 +691,12 @@
         <v>15.956172633861</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>12.609538554848511</v>
@@ -712,12 +708,12 @@
         <v>15.390025897432791</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>10.860711099859911</v>
@@ -729,12 +725,12 @@
         <v>14.493676210552829</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>7.9462559200234084</v>
@@ -746,12 +742,12 @@
         <v>12.70074398875747</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>0.25958745833038471</v>
@@ -763,12 +759,12 @@
         <v>0.56505370816478073</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>0.68608955030616237</v>
@@ -780,12 +776,12 @@
         <v>1.184326364437682</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>1.300073204785207</v>
@@ -797,12 +793,12 @@
         <v>1.9447475183788481</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>1.8096347492525979</v>
@@ -814,12 +810,12 @@
         <v>2.349939192351072</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>2.4828607823254258</v>
@@ -831,12 +827,12 @@
         <v>3.1329231897524821</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>4.0053664291923639</v>
@@ -848,12 +844,12 @@
         <v>5.0446932110316496</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>6.7731897400715804</v>
@@ -865,12 +861,12 @@
         <v>8.0974352709186288</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>10.322002799286899</v>
@@ -882,12 +878,12 @@
         <v>12.09613032609173</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>13.56546123746368</v>
@@ -899,12 +895,12 @@
         <v>15.948139022707251</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>15.93015721576306</v>
@@ -916,12 +912,12 @@
         <v>18.413800947270609</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26">
         <v>16.906196202457551</v>
@@ -933,12 +929,12 @@
         <v>19.292163451383651</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27">
         <v>16.507864328256129</v>
@@ -950,12 +946,12 @@
         <v>19.245653150059589</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28">
         <v>15.07080599624784</v>
@@ -967,12 +963,12 @@
         <v>19.205366575497841</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>11.76478451211371</v>
@@ -990,36 +986,36 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F09D7B2-3781-4472-A649-81721A75A739}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
       <c r="C2">
         <v>0.41863411170945442</v>
@@ -1031,12 +1027,12 @@
         <v>1.009212197290219</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>0.64160419263832613</v>
@@ -1048,12 +1044,12 @@
         <v>1.0859005730965829</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>1.0291784159122861</v>
@@ -1065,12 +1061,12 @@
         <v>1.715208202229241</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>1.706609771312573</v>
@@ -1082,12 +1078,12 @@
         <v>2.3823945951274248</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>2.8391017232157192</v>
@@ -1099,12 +1095,12 @@
         <v>3.705411949920868</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>4.4653977849152264</v>
@@ -1116,12 +1112,12 @@
         <v>5.7159151702476398</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>6.3592440626548257</v>
@@ -1133,12 +1129,12 @@
         <v>7.6579634547384643</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>8.3386543640890611</v>
@@ -1150,12 +1146,12 @@
         <v>9.7962101581763221</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>10.049231974616781</v>
@@ -1167,12 +1163,12 @@
         <v>11.949671547405471</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>11.37514025710052</v>
@@ -1184,12 +1180,12 @@
         <v>13.492183492165591</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>12.07948054511504</v>
@@ -1201,12 +1197,12 @@
         <v>14.284805363327891</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>12.119323075850509</v>
@@ -1218,12 +1214,12 @@
         <v>14.76888785656239</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>11.697451108196541</v>
@@ -1235,12 +1231,12 @@
         <v>15.162915744343159</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>10.494465608360549</v>
@@ -1252,12 +1248,12 @@
         <v>15.616769583013941</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>0.71377631622586646</v>
@@ -1269,12 +1265,12 @@
         <v>1.3754223907830501</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>0.75611012553543644</v>
@@ -1286,12 +1282,12 @@
         <v>1.2136042677463841</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>0.83105989801073521</v>
@@ -1303,12 +1299,12 @@
         <v>1.343073797926128</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>0.99831701154278629</v>
@@ -1320,12 +1316,12 @@
         <v>1.380814894224994</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>1.5233019577385201</v>
@@ -1337,12 +1333,12 @@
         <v>1.98217177536008</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>2.7734284023074789</v>
@@ -1354,12 +1350,12 @@
         <v>3.5750589930678598</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>5.2196040433909419</v>
@@ -1371,12 +1367,12 @@
         <v>6.3186061781975136</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>8.8901010114005654</v>
@@ -1388,12 +1384,12 @@
         <v>10.42212803251789</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>12.57423375480116</v>
@@ -1405,12 +1401,12 @@
         <v>14.516773775437381</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>15.533794392340409</v>
@@ -1422,12 +1418,12 @@
         <v>17.683781527868991</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26">
         <v>17.06858415415919</v>
@@ -1439,12 +1435,12 @@
         <v>19.264452882425989</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27">
         <v>17.21071102705918</v>
@@ -1456,12 +1452,12 @@
         <v>20.137268766751479</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28">
         <v>16.11629846143353</v>
@@ -1473,12 +1469,12 @@
         <v>20.53536850026693</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>13.075632718834081</v>
@@ -1496,36 +1492,36 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FF63EE5-D579-4D8D-A3A5-90C25DAF6B53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
       <c r="C2">
         <v>0.67665662098523327</v>
@@ -1537,12 +1533,12 @@
         <v>1.361245309083168</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>0.73789804934706749</v>
@@ -1554,12 +1550,12 @@
         <v>1.1879085634739499</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>0.87046067692886575</v>
@@ -1571,12 +1567,12 @@
         <v>1.484496074065023</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>1.1330339425512821</v>
@@ -1588,12 +1584,12 @@
         <v>1.6300937667204229</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>1.7169831876157471</v>
@@ -1605,12 +1601,12 @@
         <v>2.3726136253073138</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>2.9015718089009588</v>
@@ -1622,12 +1618,12 @@
         <v>3.8465156297439562</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>4.9680463154987073</v>
@@ -1639,12 +1635,12 @@
         <v>5.9661431219053753</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>7.5389998192483239</v>
@@ -1656,12 +1652,12 @@
         <v>9.0065310211199119</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>10.11008672402898</v>
@@ -1673,12 +1669,12 @@
         <v>12.198947778957329</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>12.22369940498252</v>
@@ -1690,12 +1686,12 @@
         <v>14.68104721035197</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>13.576682034090091</v>
@@ -1707,12 +1703,12 @@
         <v>16.226310454623562</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>13.86881120387581</v>
@@ -1724,12 +1720,12 @@
         <v>16.939042884372508</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>13.48796103823125</v>
@@ -1741,12 +1737,12 @@
         <v>17.700964100852168</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>11.70089447240391</v>
@@ -1758,12 +1754,12 @@
         <v>19.008705482362078</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>0.45659606037096351</v>
@@ -1775,12 +1771,12 @@
         <v>0.94382256998732894</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>0.52490076273169006</v>
@@ -1792,12 +1788,12 @@
         <v>0.84806009352444522</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>0.75635373492083091</v>
@@ -1809,12 +1805,12 @@
         <v>1.1776683565844801</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>1.3783774111304761</v>
@@ -1826,12 +1822,12 @@
         <v>1.8400940196976541</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>2.6433805904994032</v>
@@ -1843,12 +1839,12 @@
         <v>3.494792675550487</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>4.4033902739039412</v>
@@ -1860,12 +1856,12 @@
         <v>5.6181268638334778</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>6.7397188031189197</v>
@@ -1877,12 +1873,12 @@
         <v>7.8047805930010021</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>9.0240099916990975</v>
@@ -1894,12 +1890,12 @@
         <v>10.53619713634825</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>11.22302909713877</v>
@@ -1911,12 +1907,12 @@
         <v>13.22635617472549</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>12.9359827643702</v>
@@ -1928,12 +1924,12 @@
         <v>15.275575435103629</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26">
         <v>14.079614939729661</v>
@@ -1945,12 +1941,12 @@
         <v>16.556230241512768</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27">
         <v>14.5979171185387</v>
@@ -1962,12 +1958,12 @@
         <v>17.78536636069466</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28">
         <v>14.439071204991</v>
@@ -1979,12 +1975,12 @@
         <v>19.091616094407851</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>13.343156474800621</v>
@@ -2002,36 +1998,36 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EAB0104-7223-4583-8918-FE6E021198A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
       <c r="C2">
         <v>0.25451553393621262</v>
@@ -2043,12 +2039,12 @@
         <v>0.68850100516937074</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>0.37738467619770161</v>
@@ -2060,12 +2056,12 @@
         <v>0.76542352170333017</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>0.63531741151080967</v>
@@ -2077,12 +2073,12 @@
         <v>1.0804798836979359</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>1.177505187680149</v>
@@ -2094,12 +2090,12 @@
         <v>1.686226665204789</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>2.237713697521801</v>
@@ -2111,12 +2107,12 @@
         <v>2.9418841129096061</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>3.8706189286542392</v>
@@ -2128,12 +2124,12 @@
         <v>4.9790638711440902</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>5.9266813942250502</v>
@@ -2145,12 +2141,12 @@
         <v>7.2585591571889081</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>8.0427920203087311</v>
@@ -2162,12 +2158,12 @@
         <v>9.5069269889239063</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>9.6779214854294242</v>
@@ -2179,12 +2175,12 @@
         <v>11.416871180904259</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>10.600374112306801</v>
@@ -2196,12 +2192,12 @@
         <v>12.557139295225999</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>10.65982175584452</v>
@@ -2213,12 +2209,12 @@
         <v>12.593484418230441</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>10.00196416515675</v>
@@ -2230,12 +2226,12 @@
         <v>12.056690601273541</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>8.8384047182938179</v>
@@ -2247,12 +2243,12 @@
         <v>11.507303262151551</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>6.6380143563781084</v>
@@ -2264,12 +2260,12 @@
         <v>10.844197610579981</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>0.48962790331051748</v>
@@ -2281,12 +2277,12 @@
         <v>1.335338491016534</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>0.55278951599206705</v>
@@ -2298,12 +2294,12 @@
         <v>0.98421978656879283</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>0.72714137790330857</v>
@@ -2315,12 +2311,12 @@
         <v>1.109868370936876</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>1.129038486621138</v>
@@ -2332,12 +2328,12 @@
         <v>1.484929771033642</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>1.941090137189768</v>
@@ -2349,12 +2345,12 @@
         <v>2.494685057780031</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>3.3127307813551332</v>
@@ -2366,12 +2362,12 @@
         <v>4.2625390517116353</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>5.4925594606683683</v>
@@ -2383,12 +2379,12 @@
         <v>6.7683503148711788</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>8.2061068685007452</v>
@@ -2400,12 +2396,12 @@
         <v>9.6442420924164551</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>10.805549532236549</v>
@@ -2417,12 +2413,12 @@
         <v>12.717641035388439</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>12.83607835758613</v>
@@ -2434,12 +2430,12 @@
         <v>14.937471082758471</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26">
         <v>13.84546577539534</v>
@@ -2451,12 +2447,12 @@
         <v>15.906030982524371</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27">
         <v>13.90910446155184</v>
@@ -2468,12 +2464,12 @@
         <v>16.26011582397895</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28">
         <v>13.120834265149989</v>
@@ -2485,12 +2481,12 @@
         <v>16.604666456639151</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>10.387447277692271</v>
@@ -2508,36 +2504,36 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D277C8-9E3C-4D98-A21E-380B38C6BDE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
       <c r="C2">
         <v>0.25537976057789158</v>
@@ -2549,12 +2545,12 @@
         <v>1.016761435973123</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>0.32359600445221459</v>
@@ -2566,12 +2562,12 @@
         <v>0.5897204728765516</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>0.46222548607926189</v>
@@ -2583,12 +2579,12 @@
         <v>0.8425990651032923</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>0.81479609181311186</v>
@@ -2600,12 +2596,12 @@
         <v>1.2610823225096011</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>1.5306441481586399</v>
@@ -2617,12 +2613,12 @@
         <v>2.288901882351813</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>2.644524954892947</v>
@@ -2634,12 +2630,12 @@
         <v>3.9177773197435442</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>4.1890847986804616</v>
@@ -2651,12 +2647,12 @@
         <v>5.5773519550788349</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>6.042556334970044</v>
@@ -2668,12 +2664,12 @@
         <v>7.2735658003920882</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>7.7116749166240091</v>
@@ -2685,12 +2681,12 @@
         <v>9.3933585760905913</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>8.9499442101694591</v>
@@ -2702,12 +2698,12 @@
         <v>11.129415008312449</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>9.6017700348049804</v>
@@ -2719,12 +2715,12 @@
         <v>12.15238460560669</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>9.5996790377417174</v>
@@ -2736,12 +2732,12 @@
         <v>12.1243182777868</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>8.9996369883541067</v>
@@ -2753,12 +2749,12 @@
         <v>12.142020715618839</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>7.5047818061990634</v>
@@ -2770,12 +2766,12 @@
         <v>12.172346487684409</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>0.59482633993595213</v>
@@ -2787,12 +2783,12 @@
         <v>1.7504980770967411</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>0.52008366907371106</v>
@@ -2804,12 +2800,12 @@
         <v>0.86450086355918854</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>0.55085020374626614</v>
@@ -2821,12 +2817,12 @@
         <v>0.83621361780567716</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>0.77482942514017672</v>
@@ -2838,12 +2834,12 @@
         <v>1.063850381783483</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>1.3141790594943139</v>
@@ -2855,12 +2851,12 @@
         <v>1.772113365436248</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>2.4434689959141851</v>
@@ -2872,12 +2868,12 @@
         <v>3.306360906165859</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>4.486239331721908</v>
@@ -2889,12 +2885,12 @@
         <v>5.6432933067294186</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>7.2569857005551048</v>
@@ -2906,12 +2902,12 @@
         <v>8.6272809618723638</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>10.22042636519077</v>
@@ -2923,12 +2919,12 @@
         <v>11.945362391595889</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>12.46119252999658</v>
@@ -2940,12 +2936,12 @@
         <v>14.531262783149829</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26">
         <v>13.501436624851589</v>
@@ -2957,12 +2953,12 @@
         <v>15.654620910642819</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27">
         <v>13.380612451874541</v>
@@ -2974,12 +2970,12 @@
         <v>15.81131010399092</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28">
         <v>12.155638304332321</v>
@@ -2991,12 +2987,12 @@
         <v>15.181230922180269</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>9.4781553353422705</v>
@@ -3014,36 +3010,36 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0443F0-0721-49E8-AC88-5AD721BABB3B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
       <c r="C2">
         <v>0.50455002853010011</v>
@@ -3055,12 +3051,12 @@
         <v>1.135928939382997</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>0.66455220819768013</v>
@@ -3072,12 +3068,12 @@
         <v>1.16755042447378</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>0.88486676515618234</v>
@@ -3089,12 +3085,12 @@
         <v>1.820576943669614</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>1.212664622819283</v>
@@ -3106,12 +3102,12 @@
         <v>2.036711883879915</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>1.74662007120832</v>
@@ -3123,12 +3119,12 @@
         <v>2.3869775622423139</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>2.616811331740625</v>
@@ -3140,12 +3136,12 @@
         <v>3.4961884145121749</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>3.914712562650783</v>
@@ -3157,12 +3153,12 @@
         <v>4.8754230755882162</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>5.4171618595130129</v>
@@ -3174,12 +3170,12 @@
         <v>6.5502187314255274</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>6.8822572935338648</v>
@@ -3191,12 +3187,12 @@
         <v>8.2355707499404058</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>8.0447353926821759</v>
@@ -3208,12 +3204,12 @@
         <v>9.7153498978362833</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>8.7678647725527163</v>
@@ -3225,12 +3221,12 @@
         <v>10.791032119886269</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>9.1064134310846363</v>
@@ -3242,12 +3238,12 @@
         <v>11.32907306539637</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>9.0108236938368815</v>
@@ -3259,12 +3255,12 @@
         <v>11.840258817759731</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>8.274082307359178</v>
@@ -3276,12 +3272,12 @@
         <v>13.228745911860839</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>0.30995190555808128</v>
@@ -3293,12 +3289,12 @@
         <v>1.429679388883444</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>0.46645506389326119</v>
@@ -3310,12 +3306,12 @@
         <v>0.9157534028619716</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>0.66994898476023457</v>
@@ -3327,12 +3323,12 @@
         <v>1.012139219014665</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>0.95768398179118708</v>
@@ -3344,12 +3340,12 @@
         <v>1.318309746038786</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>1.4516330699431661</v>
@@ -3361,12 +3357,12 @@
         <v>1.9173894171552841</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>2.5024206673202709</v>
@@ -3378,12 +3374,12 @@
         <v>3.2630836797901139</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>4.4867324012978393</v>
@@ -3395,12 +3391,12 @@
         <v>5.3523685057412038</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>7.0871335158595921</v>
@@ -3412,12 +3408,12 @@
         <v>8.3482774990063771</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>9.4378660618361447</v>
@@ -3429,12 +3425,12 @@
         <v>11.281587015669031</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>11.038631972203749</v>
@@ -3446,12 +3442,12 @@
         <v>13.19549904081973</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26">
         <v>11.46619394741894</v>
@@ -3463,12 +3459,12 @@
         <v>13.58185091821192</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27">
         <v>10.790557481358171</v>
@@ -3480,12 +3476,12 @@
         <v>12.876635142574131</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28">
         <v>9.2654331885329171</v>
@@ -3497,12 +3493,12 @@
         <v>11.737053612075391</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>6.5575950428744703</v>
@@ -3520,36 +3516,36 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8D2A20B-EBE6-48FB-9FDB-AA90724A36E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
       <c r="C2">
         <v>0.2432899299568638</v>
@@ -3561,12 +3557,12 @@
         <v>0.58049155316460199</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>0.2092322262111265</v>
@@ -3578,12 +3574,12 @@
         <v>0.38990287523355849</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>0.26507831899402429</v>
@@ -3595,12 +3591,12 @@
         <v>0.49599751052937491</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>0.51562954939097794</v>
@@ -3612,12 +3608,12 @@
         <v>0.75432064093176099</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>1.146458558590141</v>
@@ -3629,12 +3625,12 @@
         <v>1.588589270642524</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>2.2802374766667972</v>
@@ -3646,12 +3642,12 @@
         <v>3.165629290097312</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>4.0626322050450607</v>
@@ -3663,12 +3659,12 @@
         <v>5.2310678157207091</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>6.0045918294551397</v>
@@ -3680,12 +3676,12 @@
         <v>7.2573958505261968</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>7.9607913788018099</v>
@@ -3697,12 +3693,12 @@
         <v>9.5872430573973197</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>9.0142553905629423</v>
@@ -3714,12 +3710,12 @@
         <v>10.98264822245984</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>9.1818886444787431</v>
@@ -3731,12 +3727,12 @@
         <v>11.309443608334419</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>8.4846800302309031</v>
@@ -3748,12 +3744,12 @@
         <v>10.68244311878574</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>7.1918619178060954</v>
@@ -3765,12 +3761,12 @@
         <v>9.553231371209792</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>5.1033051994364582</v>
@@ -3782,12 +3778,12 @@
         <v>7.8666724057678206</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>0.1117546789408659</v>
@@ -3799,12 +3795,12 @@
         <v>0.36629155946307612</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>0.27252380311689373</v>
@@ -3816,12 +3812,12 @@
         <v>0.47387473256083179</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>0.4976837321284176</v>
@@ -3833,12 +3829,12 @@
         <v>0.8727830152543985</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>0.72346160308180751</v>
@@ -3850,12 +3846,12 @@
         <v>1.080378219390318</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>1.08768217743901</v>
@@ -3867,12 +3863,12 @@
         <v>1.5931898170956551</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>1.9982447255373279</v>
@@ -3884,12 +3880,12 @@
         <v>2.8418643123090819</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>3.8052707767502678</v>
@@ -3901,12 +3897,12 @@
         <v>4.8442875900308753</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>6.5383396402086458</v>
@@ -3918,12 +3914,12 @@
         <v>7.7817036854280444</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>9.3522481445589776</v>
@@ -3935,12 +3931,12 @@
         <v>11.45450400496957</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>11.427553290415609</v>
@@ -3952,12 +3948,12 @@
         <v>14.12668029690651</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26">
         <v>12.231420358879991</v>
@@ -3969,12 +3965,12 @@
         <v>15.02924982597075</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27">
         <v>11.67775223178184</v>
@@ -3986,12 +3982,12 @@
         <v>14.31522482933357</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28">
         <v>10.20534349724853</v>
@@ -4003,12 +3999,12 @@
         <v>12.898668648718219</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>7.1499048786210633</v>
@@ -4026,36 +4022,36 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C5E982-F0B2-4490-B037-79D8D378A4D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
       <c r="C2">
         <v>7.3111524600510347E-2</v>
@@ -4067,12 +4063,12 @@
         <v>0.30955456746617249</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>0.1681536652901951</v>
@@ -4084,12 +4080,12 @@
         <v>0.30092660891927769</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>0.31768953627074847</v>
@@ -4101,12 +4097,12 @@
         <v>0.60090813541270083</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>0.54669296601639195</v>
@@ -4118,12 +4114,12 @@
         <v>0.84862706612963945</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>0.95188061111025557</v>
@@ -4135,12 +4131,12 @@
         <v>1.3791151182365951</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>1.6978081399191081</v>
@@ -4152,12 +4148,12 @@
         <v>2.4364416849398598</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>2.9924430452534931</v>
@@ -4169,12 +4165,12 @@
         <v>3.9018705744595898</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>4.6927442210325108</v>
@@ -4186,12 +4182,12 @@
         <v>5.7963005341140299</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>6.5293604608356333</v>
@@ -4203,12 +4199,12 @@
         <v>8.1053991301614357</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>8.1602557263881526</v>
@@ -4220,12 +4216,12 @@
         <v>10.11626193266126</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>9.1693579446291977</v>
@@ -4237,12 +4233,12 @@
         <v>11.38672915103834</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>9.4837923993934119</v>
@@ -4254,12 +4250,12 @@
         <v>11.91969075432427</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>9.1839622018398881</v>
@@ -4271,12 +4267,12 @@
         <v>12.22861376642738</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>7.8707362190540113</v>
@@ -4288,12 +4284,12 @@
         <v>12.562831410052899</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>0.26657157795149838</v>
@@ -4305,12 +4301,12 @@
         <v>0.66971248372716141</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>0.36252512873050657</v>
@@ -4322,12 +4318,12 @@
         <v>0.60247089894113559</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>0.50516319253390751</v>
@@ -4339,12 +4335,12 @@
         <v>0.82840356247960489</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>0.75803477157203303</v>
@@ -4356,12 +4352,12 @@
         <v>1.054192558573267</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>1.2662276121744069</v>
@@ -4373,12 +4369,12 @@
         <v>1.6850915719662669</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>2.198441722749704</v>
@@ -4390,12 +4386,12 @@
         <v>2.846991982899715</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>3.7610183985120171</v>
@@ -4407,12 +4403,12 @@
         <v>4.593930918425472</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>5.7515342715480076</v>
@@ -4424,12 +4420,12 @@
         <v>6.8018030675949319</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>7.62577741947183</v>
@@ -4441,12 +4437,12 @@
         <v>9.0772289854030515</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>9.0101659684113393</v>
@@ -4458,12 +4454,12 @@
         <v>10.734513327706971</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26">
         <v>9.6657859242454922</v>
@@ -4475,12 +4471,12 @@
         <v>11.61046301875122</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27">
         <v>9.466841463690189</v>
@@ -4492,12 +4488,12 @@
         <v>11.682652387179781</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28">
         <v>8.725196251026448</v>
@@ -4509,12 +4505,12 @@
         <v>11.41532253970168</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>6.829026769499869</v>
